--- a/artfynd/A 43426-2023 artfynd.xlsx
+++ b/artfynd/A 43426-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1155,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126092866</v>
+        <v>134500144</v>
       </c>
       <c r="B6" t="n">
-        <v>58393</v>
+        <v>58563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,16 +1166,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102999</v>
+        <v>102987</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690602</v>
+        <v>690607</v>
       </c>
       <c r="R6" t="n">
-        <v>7080999</v>
+        <v>7081010</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,22 +1228,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126092865</v>
+        <v>126092866</v>
       </c>
       <c r="B7" t="n">
-        <v>58388</v>
+        <v>58393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,32 +1385,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126111879</v>
+        <v>134500140</v>
       </c>
       <c r="B8" t="n">
-        <v>58439</v>
+        <v>58415</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103018</v>
+        <v>102999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1419,16 +1419,8 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1466,22 +1458,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,10 +1500,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122716049</v>
+        <v>126092865</v>
       </c>
       <c r="B9" t="n">
-        <v>58114</v>
+        <v>58388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,26 +1511,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1551,13 +1543,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>690607</v>
+        <v>690602</v>
       </c>
       <c r="R9" t="n">
-        <v>7081010</v>
+        <v>7080999</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1581,22 +1573,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,42 +1615,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130287917</v>
+        <v>126111879</v>
       </c>
       <c r="B10" t="n">
-        <v>58057</v>
+        <v>58439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>103018</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1696,22 +1696,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130290785</v>
+        <v>122716049</v>
       </c>
       <c r="B11" t="n">
-        <v>58057</v>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1749,21 +1749,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1773,11 +1773,7 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1785,13 +1781,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690600</v>
+        <v>690607</v>
       </c>
       <c r="R11" t="n">
-        <v>7080982</v>
+        <v>7081010</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,22 +1811,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-02-23</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2025-02-23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,27 +1853,27 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126092870</v>
+        <v>130287917</v>
       </c>
       <c r="B12" t="n">
-        <v>58636</v>
+        <v>58057</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103044</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1887,7 +1883,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1900,13 +1896,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690602</v>
+        <v>690607</v>
       </c>
       <c r="R12" t="n">
-        <v>7080999</v>
+        <v>7081010</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1930,22 +1926,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,6 +1965,355 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130290785</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mjösjö 1 gården, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>690600</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7080982</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ann-Katrin AX Sjögren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ann-Katrin AX Sjögren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126092870</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mjösjö 1 gården, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>690602</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7080999</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Ann-Katrin AX Sjögren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Ann-Katrin AX Sjögren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134500148</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mjösjö 1 gården, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>690607</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7081010</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Ann-Katrin AX Sjögren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Ann-Katrin AX Sjögren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43426-2023 artfynd.xlsx
+++ b/artfynd/A 43426-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2315,6 +2315,125 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134541776</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58107</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mjösjö 1 gården, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>690600</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7080982</v>
+      </c>
+      <c r="S16" t="n">
+        <v>8</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ann-Katrin AX Sjögren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ann-Katrin AX Sjögren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43426-2023 artfynd.xlsx
+++ b/artfynd/A 43426-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126132737</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126976636</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130290783</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1152,6 +1172,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126092868</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134500144</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126092866</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1497,6 +1532,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134500140</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1612,6 +1652,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126092865</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1735,6 +1780,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126111879</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1850,6 +1900,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122716049</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1965,6 +2020,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130287917</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2084,6 +2144,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130290785</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2199,6 +2264,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126092870</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2314,6 +2384,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134500148</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2433,8 +2508,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134541776</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>